--- a/Taetigkeitsuebersicht_Julia.xlsx
+++ b/Taetigkeitsuebersicht_Julia.xlsx
@@ -159,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +202,16 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -567,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -675,39 +685,583 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="C11" s="6" t="inlineStr">
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>10.02.2026</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>Kick-off-Meeting: Projektidee BESE.CO besprochen, Rolle als QA übernommen, Testkonzept skizziert</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Vincent, Angelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>24.03.2026</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="inlineStr">
+        <is>
+          <t>Meilenstein-Review: Registrierung und Login-System gemeinsam mit Vincent und Angelo getestet</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Vincent, Angelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Meilenstein-Review: Produktkatalog und Warenkorb-Funktionalität geprüft und Feedback gegeben</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Vincent, Angelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>14.04.2026</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>Backend-Test: Bestellprozess manuell durchgespielt, Transaktionsverhalten beobachtet</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>21.04.2026</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Checkout-Prozess getestet: Zahlungsmethoden und Live-Zusammenfassung auf Korrektheit geprüft</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="inlineStr">
+        <is>
+          <t>Testplanung: Testfälle TF-001 bis TF-006 mit Vincent definiert, Testdaten und Voraussetzungen dokumentiert</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>03.05.2026</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>TF-001: Datenbankverbindung und Fehlerbehandlung bei DB-Ausfall getestet. Fehler: PHP Fatal Error bei deaktiviertem MySQL</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>03.05.2026</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>Fehlerbericht TF-001 an Angelo kommuniziert, Try-Catch-Lösung besprochen</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>03.05.2026</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>TF-002: Validierung von DB-Einträgen (NULL-Preise, negative Mengen). Fehler: Leeres Preisfeld, negative Mengen akzeptiert</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>03.05.2026</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="inlineStr">
+        <is>
+          <t>Fehlerbericht TF-002 an Angelo kommuniziert, Validierungslösung besprochen</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>03.05.2026</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Re-Test TF-001 und TF-002 nach Bugfix: Beide Fehler behoben, Ergebnisse im Testprotokoll dokumentiert</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>TF-003: Duplikatprüfung bei Registrierung mit existierender E-Mail getestet. Ergebnis: Bestanden</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>TF-004: End-to-End Bestellprozess (Login, Produktauswahl, Warenkorb, Checkout, DB-Prüfung). Ergebnis: Bestanden</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>04.05.2026</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>Feedback an Angelo: Optisches Feedback bei Bestellbestätigung verbessern</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Angelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>TF-005: Checkout mit allen 4 Zahlungsmethoden (Rechnung, PayPal, Kreditkarte, Vorkasse). Ergebnis: Bestanden</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>05.05.2026</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>TF-006: Bestellstornierung mit Lagerbestandswiederherstellung, Sicherheitsprüfung. Ergebnis: Bestanden</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>07.05.2026</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>Testprotokoll finalisiert, Kommunikationslogbuch vervollständigt, Abgabe vorbereitet</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Keine</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>Gesamt:</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
     </row>
@@ -849,7 +1403,7 @@
           <t>Hat die Projektstruktur mitdefiniert und auf Konsistenz geachtet.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="12" t="n"/>
       <c r="F9" s="15" t="n">
         <v>4</v>
       </c>
@@ -890,7 +1444,7 @@
           <t>Review-Feedback hat zu besserer Kommentierung geführt.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="12" t="n"/>
       <c r="F11" s="15" t="n">
         <v>3</v>
       </c>
@@ -931,7 +1485,7 @@
           <t>Datenbankschema im Review geprüft und Verbesserungen vorgeschlagen.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="12" t="n"/>
       <c r="F13" s="15" t="n">
         <v>4</v>
       </c>
@@ -972,7 +1526,7 @@
           <t>Alle Meilensteine kontrolliert und Qualität sichergestellt.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="12" t="n"/>
       <c r="F15" s="15" t="n">
         <v>4</v>
       </c>
@@ -1081,7 +1635,7 @@
           <t>Deckblatt-Vorlage vorgegeben, ansprechend.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="12" t="n"/>
       <c r="F22" s="15" t="n">
         <v>3</v>
       </c>
@@ -1123,7 +1677,7 @@
           <t>Gliederung vorgegeben und kontrolliert.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
+      <c r="E24" s="12" t="n"/>
       <c r="F24" s="15" t="n">
         <v>4</v>
       </c>
@@ -1164,7 +1718,7 @@
           <t>Projektbeschreibung vollständig, gute Struktur.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="12" t="n"/>
       <c r="F26" s="15" t="n">
         <v>4</v>
       </c>
@@ -1206,7 +1760,7 @@
           <t>Implementierungsbeschreibung geprüft und Feedback gegeben.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="12" t="n"/>
       <c r="F28" s="15" t="n">
         <v>3</v>
       </c>
@@ -1248,7 +1802,7 @@
           <t>Fazit und Ausblick sinnvoll formuliert.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="12" t="n"/>
       <c r="F30" s="15" t="n">
         <v>4</v>
       </c>
@@ -1358,7 +1912,7 @@
           <t>Koordiniert das Team vorbildlich, regelmäßige Meetings organisiert.</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="12" t="n"/>
       <c r="F37" s="15" t="n">
         <v>4</v>
       </c>
@@ -1399,7 +1953,7 @@
           <t>Gutes Gesamtverständnis, kann Zusammenhänge gut erklären.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
+      <c r="E39" s="12" t="n"/>
       <c r="F39" s="15" t="n">
         <v>4</v>
       </c>
@@ -1508,7 +2062,7 @@
           <t>Alle Meetings und Reviews dokumentiert.</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
+      <c r="E46" s="12" t="n"/>
       <c r="F46" s="15" t="n">
         <v>4</v>
       </c>
@@ -1550,7 +2104,7 @@
           <t>Tätigkeiten nachvollziehbar beschrieben, Abstimmung mit Team erkennbar.</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="12" t="n"/>
       <c r="F48" s="15" t="n">
         <v>3</v>
       </c>
@@ -1678,10 +2232,10 @@
           <t>4. Tätigkeitsbericht (IN)</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="29" t="n"/>
       <c r="F57" s="15" t="n">
         <v>1.9</v>
       </c>
@@ -1713,8 +2267,8 @@
   <mergeCells count="18">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D11:E11"/>
@@ -1867,7 +2421,7 @@
           <t>Sauberer, gut strukturierter Code mit konsistenter Einrückung. Projektstruktur klar und modular aufgebaut.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n"/>
+      <c r="E9" s="12" t="n"/>
       <c r="F9" s="15" t="n">
         <v>4</v>
       </c>
@@ -1908,7 +2462,7 @@
           <t>Wichtige Funktionen kommentiert, config.php und order.php gut dokumentiert.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n"/>
+      <c r="E11" s="12" t="n"/>
       <c r="F11" s="15" t="n">
         <v>3</v>
       </c>
@@ -1949,7 +2503,7 @@
           <t>ERM-Diagramm vollständig, SQL-Skript sauber mit PK/FK/UNIQUE. Klare Benennung.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n"/>
+      <c r="E13" s="12" t="n"/>
       <c r="F13" s="15" t="n">
         <v>4</v>
       </c>
@@ -1990,7 +2544,7 @@
           <t>Alle Kernfeatures implementiert und funktionsfähig. Warenkorb, Checkout und Stornierung laufen fehlerfrei.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="12" t="n"/>
       <c r="F15" s="15" t="n">
         <v>4</v>
       </c>
@@ -2099,7 +2653,7 @@
           <t>Übersichtlich gestaltet, alle Infos vorhanden.</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n"/>
+      <c r="E22" s="12" t="n"/>
       <c r="F22" s="15" t="n">
         <v>3</v>
       </c>
@@ -2141,7 +2695,7 @@
           <t>Vollständig mit Seitenzahlen und Gliederung.</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n"/>
+      <c r="E24" s="12" t="n"/>
       <c r="F24" s="15" t="n">
         <v>4</v>
       </c>
@@ -2182,7 +2736,7 @@
           <t>Ausgangssituation, Zielsetzung und Technologien ausführlich beschrieben.</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n"/>
+      <c r="E26" s="12" t="n"/>
       <c r="F26" s="15" t="n">
         <v>4</v>
       </c>
@@ -2224,7 +2778,7 @@
           <t>Screenshots und Code-Beispiele vorhanden, Bestellablauf gut erklärt.</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n"/>
+      <c r="E28" s="12" t="n"/>
       <c r="F28" s="15" t="n">
         <v>3</v>
       </c>
@@ -2266,7 +2820,7 @@
           <t>Probleme und Lösungen dokumentiert, Testprotokoll angehängt, Erweiterungen genannt.</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="12" t="n"/>
       <c r="F30" s="15" t="n">
         <v>4</v>
       </c>
@@ -2376,7 +2930,7 @@
           <t>Sehr aktiv in Meetings, hat alle Bugfixes zeitnah umgesetzt.</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="12" t="n"/>
       <c r="F37" s="15" t="n">
         <v>4</v>
       </c>
@@ -2417,7 +2971,7 @@
           <t>Sehr gutes technisches Verständnis, kann Architekturentscheidungen erklären.</t>
         </is>
       </c>
-      <c r="E39" s="5" t="n"/>
+      <c r="E39" s="12" t="n"/>
       <c r="F39" s="15" t="n">
         <v>4</v>
       </c>
@@ -2526,7 +3080,7 @@
           <t>Alle Arbeitstage lückenlos dokumentiert.</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n"/>
+      <c r="E46" s="12" t="n"/>
       <c r="F46" s="15" t="n">
         <v>4</v>
       </c>
@@ -2568,7 +3122,7 @@
           <t>Detaillierte Beschreibung jeder Implementierung mit technischen Details.</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="12" t="n"/>
       <c r="F48" s="15" t="n">
         <v>4</v>
       </c>
@@ -2696,10 +3250,10 @@
           <t>4. Tätigkeitsbericht (IN)</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="5" t="n"/>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="28" t="n"/>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="29" t="n"/>
       <c r="F57" s="15" t="n">
         <v>1</v>
       </c>
@@ -2731,8 +3285,8 @@
   <mergeCells count="18">
     <mergeCell ref="D20:E20"/>
     <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D30:E30"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D11:E11"/>
